--- a/data/processed/positivacao/2026-07_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2026-07_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -27311,7 +27311,7 @@
     <row r="1038">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B1038" t="inlineStr"/>
@@ -35881,7 +35881,7 @@
     <row r="1368">
       <c r="A1368" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1368" t="inlineStr"/>
@@ -66307,7 +66307,7 @@
     <row r="2539">
       <c r="A2539" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2539" t="inlineStr"/>
@@ -67952,12 +67952,12 @@
       <c r="A2603" t="inlineStr"/>
       <c r="B2603" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 3 cliente(s), não positivou 83 cliente(s) - Total vendido: R$ 2.678,95
+          <t>Vendedor 1 - VENDEDOR 01: positivou 3 cliente(s), não positivou 83 cliente(s) - Total vendido: R$ 2.678,95
 Vendedor 18 - LOJA: positivou 297 cliente(s), não positivou 645 cliente(s) - Total vendido: R$ 98.460,80
-Vendedor 3 - FERNANDA: positivou 2 cliente(s), não positivou 327 cliente(s) - Total vendido: R$ 723,66
-Vendedor 4 - DANIELA: positivou 231 cliente(s), não positivou 492 cliente(s) - Total vendido: R$ 242.375,68
+Vendedor 3 - VENDEDOR 03: positivou 2 cliente(s), não positivou 327 cliente(s) - Total vendido: R$ 723,66
+Vendedor 4 - VENDEDOR 04: positivou 231 cliente(s), não positivou 492 cliente(s) - Total vendido: R$ 242.375,68
 Vendedor 5 - SITE: positivou 4 cliente(s), não positivou 442 cliente(s) - Total vendido: R$ 941,15
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 62 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 62 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2603" t="inlineStr"/>
